--- a/data/trans_dic/P1428-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1428-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 17,99</t>
+          <t>13,68; 17,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 13,91</t>
+          <t>9,55; 13,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,27</t>
+          <t>6,32; 10,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 15,4</t>
+          <t>10,05; 14,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,83; 37,89</t>
+          <t>32,85; 37,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 27,05</t>
+          <t>22,19; 27,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 23,88</t>
+          <t>18,3; 23,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,88; 36,56</t>
+          <t>30,38; 35,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,92; 28,52</t>
+          <t>25,03; 28,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,63; 20,87</t>
+          <t>17,56; 20,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 17,37</t>
+          <t>13,55; 17,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,29; 27,3</t>
+          <t>22,56; 26,14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,77</t>
+          <t>2,81; 4,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,41</t>
+          <t>1,96; 3,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,17</t>
+          <t>1,77; 3,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,94</t>
+          <t>3,64; 5,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,1</t>
+          <t>5,44; 7,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,16</t>
+          <t>3,89; 6,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 6,38</t>
+          <t>4,34; 6,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 39,67</t>
+          <t>8,67; 10,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 5,93</t>
+          <t>4,39; 5,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,36</t>
+          <t>3,11; 4,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,44</t>
+          <t>3,22; 4,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 26,16</t>
+          <t>6,37; 7,67</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,18</t>
+          <t>1,34; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,61</t>
+          <t>1,07; 4,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,28</t>
+          <t>0,72; 3,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,01</t>
+          <t>1,71; 4,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,65</t>
+          <t>3,55; 7,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,84</t>
+          <t>3,12; 7,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,94</t>
+          <t>1,64; 4,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,32</t>
+          <t>6,17; 9,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,41</t>
+          <t>2,7; 5,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,35</t>
+          <t>2,4; 5,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,5</t>
+          <t>1,53; 3,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,14</t>
+          <t>4,26; 6,3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,15</t>
+          <t>6,46; 8,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,05</t>
+          <t>4,4; 5,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,22</t>
+          <t>2,98; 4,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,89</t>
+          <t>4,63; 6,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,97</t>
+          <t>16,39; 19,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 13,54</t>
+          <t>11,17; 13,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,41</t>
+          <t>8,41; 10,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,98; 32,95</t>
+          <t>13,49; 15,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 13,36</t>
+          <t>11,69; 13,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,59</t>
+          <t>8,15; 9,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,1</t>
+          <t>5,95; 7,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 21,29</t>
+          <t>9,36; 10,59</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65537</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>252506</t>
+          <t>268291</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>318043</t>
+          <t>337971</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>139480; 185580</t>
+          <t>141136; 185334</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95984; 135542</t>
+          <t>93110; 135571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46105; 77493</t>
+          <t>47699; 75886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53087; 78504</t>
+          <t>57610; 83959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>431727; 498271</t>
+          <t>432009; 498910</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>300354; 361844</t>
+          <t>296811; 363440</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>181197; 237516</t>
+          <t>181994; 235607</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>231322; 273894</t>
+          <t>248063; 288862</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>584878; 669392</t>
+          <t>587399; 669887</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>407692; 482501</t>
+          <t>406144; 483635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>237018; 303805</t>
+          <t>237021; 299842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>293177; 343747</t>
+          <t>313424; 363160</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91826</t>
+          <t>97150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>394222</t>
+          <t>208682</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>486048</t>
+          <t>305831</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48113; 80757</t>
+          <t>47614; 77423</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36975; 66984</t>
+          <t>38479; 67361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36455; 65750</t>
+          <t>36791; 66405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62815; 112959</t>
+          <t>81107; 115831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86341; 128565</t>
+          <t>86334; 126870</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67187; 108017</t>
+          <t>68237; 108083</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86842; 126837</t>
+          <t>86293; 129156</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>198553; 883968</t>
+          <t>187448; 233225</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>144577; 194422</t>
+          <t>143921; 194594</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116158; 161979</t>
+          <t>115668; 165674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131231; 180438</t>
+          <t>130892; 179630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>279537; 1181824</t>
+          <t>279724; 336645</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49120</t>
+          <t>56432</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65322</t>
+          <t>74708</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7622; 23029</t>
+          <t>7372; 23275</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5266; 22161</t>
+          <t>5153; 21836</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4337; 17943</t>
+          <t>3962; 18985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9783; 25916</t>
+          <t>12121; 28484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16173; 36469</t>
+          <t>16925; 38065</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15267; 35958</t>
+          <t>14299; 35067</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9497; 27111</t>
+          <t>8985; 26802</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39145; 61503</t>
+          <t>45282; 69095</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28410; 55592</t>
+          <t>27756; 52929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23301; 50309</t>
+          <t>22567; 50040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16601; 38396</t>
+          <t>16798; 38827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>52926; 80205</t>
+          <t>61573; 90967</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>695848</t>
+          <t>533404</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>869412</t>
+          <t>718511</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>208868; 267097</t>
+          <t>211644; 267642</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>150943; 207038</t>
+          <t>150335; 204273</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100992; 142484</t>
+          <t>100612; 145376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135962; 202740</t>
+          <t>162649; 211727</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>552263; 640890</t>
+          <t>553969; 642144</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>403268; 480783</t>
+          <t>396547; 477749</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>296649; 367617</t>
+          <t>297150; 369630</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>508449; 1198681</t>
+          <t>500649; 567093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>777516; 889127</t>
+          <t>778081; 889635</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>569110; 668259</t>
+          <t>568330; 663921</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>404409; 490277</t>
+          <t>410885; 493584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>656534; 1507587</t>
+          <t>676088; 764774</t>
         </is>
       </c>
     </row>
